--- a/assets/sample.xlsx
+++ b/assets/sample.xlsx
@@ -4271,8 +4271,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010023107A54E8B8B9488EB77197E8D12F37" ma:contentTypeVersion="11" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="8d358518067bbe07db32bef8a7675f16">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fe95f226-17bd-48ac-b121-8b008b204525" xmlns:ns3="f1c2b24c-1bef-4db6-ac93-0552d2349689" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5d9719c90ba3395da330de7fcde79a24" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010023107A54E8B8B9488EB77197E8D12F37" ma:contentTypeVersion="11" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="e5c38d44df2b44e63399d3149ec89ef1">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fe95f226-17bd-48ac-b121-8b008b204525" xmlns:ns3="f1c2b24c-1bef-4db6-ac93-0552d2349689" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="86f85a61143a6e528cde30bd9651738c" ns2:_="" ns3:_="">
     <xsd:import namespace="fe95f226-17bd-48ac-b121-8b008b204525"/>
     <xsd:import namespace="f1c2b24c-1bef-4db6-ac93-0552d2349689"/>
     <xsd:element name="properties">
@@ -4486,7 +4486,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{005973AB-89A3-45D7-8BEA-B68D748659DD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0C49A74-8F07-425A-86D2-EC655CE4E709}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
